--- a/results/07-2025/beta/contributions-07-2025.xlsx
+++ b/results/07-2025/beta/contributions-07-2025.xlsx
@@ -22259,7 +22259,7 @@
         <v>0</v>
       </c>
       <c r="D223" t="n">
-        <v>-0.250199510132909</v>
+        <v>-0.218091441390802</v>
       </c>
       <c r="E223" t="n">
         <v>-0.199879916241108</v>
@@ -22316,13 +22316,13 @@
         <v>-0.00151505975298941</v>
       </c>
       <c r="W223" t="n">
-        <v>0.243428195800901</v>
+        <v>0.242347826012976</v>
       </c>
       <c r="X223" t="n">
-        <v>-0.00627217178817736</v>
+        <v>-0.00677250107663066</v>
       </c>
       <c r="Y223" t="n">
-        <v>-0.452964229106557</v>
+        <v>-0.420856160364451</v>
       </c>
       <c r="Z223" t="n">
         <v>0.00288480273254083</v>
@@ -22331,16 +22331,16 @@
         <v>-0.088289444952879</v>
       </c>
       <c r="AB223" t="n">
-        <v>0.136614390202252</v>
+        <v>0.135033221417888</v>
       </c>
       <c r="AC223" t="n">
-        <v>-0.951548611628606</v>
+        <v>-0.953131244205811</v>
       </c>
       <c r="AD223" t="n">
-        <v>-1.40162803800262</v>
+        <v>-1.37110260183772</v>
       </c>
       <c r="AE223" t="n">
-        <v>-0.265403650799482</v>
+        <v>-0.257772291758256</v>
       </c>
     </row>
     <row r="224">
@@ -22354,7 +22354,7 @@
         <v>0</v>
       </c>
       <c r="D224" t="n">
-        <v>-0.166032314733355</v>
+        <v>-0.166335102426299</v>
       </c>
       <c r="E224" t="n">
         <v>-0.188402753588166</v>
@@ -22366,7 +22366,7 @@
         <v>-0.00499532512598115</v>
       </c>
       <c r="H224" t="n">
-        <v>-0.0395148927973874</v>
+        <v>0.141866401137088</v>
       </c>
       <c r="I224" t="n">
         <v>0.185730312532247</v>
@@ -22411,31 +22411,31 @@
         <v>-0.000451773171946533</v>
       </c>
       <c r="W224" t="n">
-        <v>0.172464448233597</v>
+        <v>0.170312754424817</v>
       </c>
       <c r="X224" t="n">
-        <v>0.0167197530513641</v>
+        <v>0.0157297326996495</v>
       </c>
       <c r="Y224" t="n">
-        <v>-0.219157634022844</v>
+        <v>-0.219460421715788</v>
       </c>
       <c r="Z224" t="n">
         <v>-0.135277434298677</v>
       </c>
       <c r="AA224" t="n">
-        <v>0.104538323808508</v>
+        <v>0.285644148739794</v>
       </c>
       <c r="AB224" t="n">
-        <v>0.121299413270645</v>
+        <v>0.118157605258083</v>
       </c>
       <c r="AC224" t="n">
-        <v>-0.774296001511843</v>
+        <v>-0.596554324326954</v>
       </c>
       <c r="AD224" t="n">
-        <v>-1.12873106983336</v>
+        <v>-0.951292180341419</v>
       </c>
       <c r="AE224" t="n">
-        <v>-0.672944430770533</v>
+        <v>-0.620953349356321</v>
       </c>
     </row>
     <row r="225">
@@ -22449,7 +22449,7 @@
         <v>0</v>
       </c>
       <c r="D225" t="n">
-        <v>0.0253758993631041</v>
+        <v>0.138347808668163</v>
       </c>
       <c r="E225" t="n">
         <v>-0.187426688324483</v>
@@ -22461,7 +22461,7 @@
         <v>-0.0153552438046491</v>
       </c>
       <c r="H225" t="n">
-        <v>-0.0358643867623123</v>
+        <v>0.140377254322351</v>
       </c>
       <c r="I225" t="n">
         <v>0.0729643688673298</v>
@@ -22470,7 +22470,7 @@
         <v>0.00545401864232233</v>
       </c>
       <c r="K225" t="n">
-        <v>-0.0186080156825595</v>
+        <v>-0.0366943534705917</v>
       </c>
       <c r="L225" t="n">
         <v>0.0314648671659881</v>
@@ -22506,31 +22506,31 @@
         <v>-0.000419227109622843</v>
       </c>
       <c r="W225" t="n">
-        <v>0.121072944906745</v>
+        <v>0.129494712030853</v>
       </c>
       <c r="X225" t="n">
-        <v>0.033558144442533</v>
+        <v>0.0374417781397447</v>
       </c>
       <c r="Y225" t="n">
-        <v>-0.080169532365765</v>
+        <v>0.0328023769392936</v>
       </c>
       <c r="Z225" t="n">
         <v>-0.0818812565956142</v>
       </c>
       <c r="AA225" t="n">
-        <v>0.0215189867322611</v>
+        <v>0.197653824473987</v>
       </c>
       <c r="AB225" t="n">
-        <v>0.0906350601298607</v>
+        <v>0.0848773632426025</v>
       </c>
       <c r="AC225" t="n">
-        <v>-0.88786655633996</v>
+        <v>-0.717646085911434</v>
       </c>
       <c r="AD225" t="n">
-        <v>-1.04991734530134</v>
+        <v>-0.766724965567754</v>
       </c>
       <c r="AE225" t="n">
-        <v>-1.02334708307678</v>
+        <v>-0.900557906729174</v>
       </c>
     </row>
     <row r="226">
@@ -22544,19 +22544,19 @@
         <v>0</v>
       </c>
       <c r="D226" t="n">
-        <v>-0.149403326737253</v>
+        <v>0.182123494913557</v>
       </c>
       <c r="E226" t="n">
         <v>-0.186244865759511</v>
       </c>
       <c r="F226" t="n">
-        <v>0.306590654627882</v>
+        <v>0.141087528212335</v>
       </c>
       <c r="G226" t="n">
         <v>-0.0206587577015947</v>
       </c>
       <c r="H226" t="n">
-        <v>-0.0215016380398408</v>
+        <v>0.0352176317081096</v>
       </c>
       <c r="I226" t="n">
         <v>0.316467212868588</v>
@@ -22565,7 +22565,7 @@
         <v>0.00364314963120222</v>
       </c>
       <c r="K226" t="n">
-        <v>-0.163729181568732</v>
+        <v>-0.175460839059818</v>
       </c>
       <c r="L226" t="n">
         <v>0.0385868919646275</v>
@@ -22601,31 +22601,31 @@
         <v>-0.000388464898983852</v>
       </c>
       <c r="W226" t="n">
-        <v>0.116596252482861</v>
+        <v>0.135514231959327</v>
       </c>
       <c r="X226" t="n">
-        <v>-0.0136242291221517</v>
+        <v>-0.00480605503782594</v>
       </c>
       <c r="Y226" t="n">
-        <v>-0.201939285491737</v>
+        <v>0.129587536159072</v>
       </c>
       <c r="Z226" t="n">
         <v>-0.133708907005026</v>
       </c>
       <c r="AA226" t="n">
-        <v>0.583762092627697</v>
+        <v>0.475201884951763</v>
       </c>
       <c r="AB226" t="n">
-        <v>-0.0661469008035539</v>
+        <v>-0.0500870100151668</v>
       </c>
       <c r="AC226" t="n">
-        <v>-0.481975077553002</v>
+        <v>-0.574632611434394</v>
       </c>
       <c r="AD226" t="n">
-        <v>-0.817623270049766</v>
+        <v>-0.578753982280349</v>
       </c>
       <c r="AE226" t="n">
-        <v>-1.09947493079677</v>
+        <v>-0.916968432506811</v>
       </c>
     </row>
     <row r="227">
@@ -22639,19 +22639,19 @@
         <v>0</v>
       </c>
       <c r="D227" t="n">
-        <v>-0.150854113272481</v>
+        <v>-0.091179211129241</v>
       </c>
       <c r="E227" t="n">
         <v>-0.197303734077729</v>
       </c>
       <c r="F227" t="n">
-        <v>0.277658697237849</v>
+        <v>0.114356039802799</v>
       </c>
       <c r="G227" t="n">
         <v>-0.00901379205779021</v>
       </c>
       <c r="H227" t="n">
-        <v>-0.0222887098182955</v>
+        <v>0.0330798926987005</v>
       </c>
       <c r="I227" t="n">
         <v>0.251039235479208</v>
@@ -22660,7 +22660,7 @@
         <v>0.00487621229521312</v>
       </c>
       <c r="K227" t="n">
-        <v>-0.163385782850788</v>
+        <v>-0.168986483119721</v>
       </c>
       <c r="L227" t="n">
         <v>0.0110356741019841</v>
@@ -22696,31 +22696,31 @@
         <v>-0.000339139413338695</v>
       </c>
       <c r="W227" t="n">
-        <v>0.047091497868414</v>
+        <v>0.0952519114350495</v>
       </c>
       <c r="X227" t="n">
-        <v>0.0203155642193202</v>
+        <v>0.0168723614178661</v>
       </c>
       <c r="Y227" t="n">
-        <v>-0.236149513539501</v>
+        <v>-0.176474611396261</v>
       </c>
       <c r="Z227" t="n">
         <v>-0.11200833381071</v>
       </c>
       <c r="AA227" t="n">
-        <v>0.501680247177725</v>
+        <v>0.393923358464019</v>
       </c>
       <c r="AB227" t="n">
-        <v>-0.118160783171558</v>
+        <v>-0.0789579260105366</v>
       </c>
       <c r="AC227" t="n">
-        <v>0.384147573811116</v>
+        <v>0.315294958430772</v>
       </c>
       <c r="AD227" t="n">
-        <v>0.0359897264609053</v>
+        <v>0.0268120132238019</v>
       </c>
       <c r="AE227" t="n">
-        <v>-0.740070489680891</v>
+        <v>-0.56748977874143</v>
       </c>
     </row>
     <row r="228">
@@ -22734,19 +22734,19 @@
         <v>0</v>
       </c>
       <c r="D228" t="n">
-        <v>-0.142450451880153</v>
+        <v>-0.0711419432935427</v>
       </c>
       <c r="E228" t="n">
         <v>-0.187119724943941</v>
       </c>
       <c r="F228" t="n">
-        <v>0.151678303472226</v>
+        <v>0.0724111854320921</v>
       </c>
       <c r="G228" t="n">
         <v>0.00509242029859333</v>
       </c>
       <c r="H228" t="n">
-        <v>-0.0103979632781975</v>
+        <v>0.0432668687960049</v>
       </c>
       <c r="I228" t="n">
         <v>0.0775952242339403</v>
@@ -22755,7 +22755,7 @@
         <v>0.00640109336423803</v>
       </c>
       <c r="K228" t="n">
-        <v>-0.163850551205058</v>
+        <v>-0.163478264136423</v>
       </c>
       <c r="L228" t="n">
         <v>0.0112179112527027</v>
@@ -22791,31 +22791,31 @@
         <v>-0.000331243183112972</v>
       </c>
       <c r="W228" t="n">
-        <v>0.0380058951204738</v>
+        <v>0.0973185863976518</v>
       </c>
       <c r="X228" t="n">
-        <v>0.0167627773070017</v>
+        <v>0.018809714516209</v>
       </c>
       <c r="Y228" t="n">
-        <v>-0.177038582156692</v>
+        <v>-0.105730073570082</v>
       </c>
       <c r="Z228" t="n">
         <v>-0.152531594667403</v>
       </c>
       <c r="AA228" t="n">
-        <v>0.230241981603341</v>
+        <v>0.204613883045715</v>
       </c>
       <c r="AB228" t="n">
-        <v>-0.13425725627333</v>
+        <v>-0.0724148963587344</v>
       </c>
       <c r="AC228" t="n">
-        <v>0.0963138581444369</v>
+        <v>0.132356762228991</v>
       </c>
       <c r="AD228" t="n">
-        <v>-0.233256318679658</v>
+        <v>-0.125904906008493</v>
       </c>
       <c r="AE228" t="n">
-        <v>-0.516201801892465</v>
+        <v>-0.361142960158199</v>
       </c>
     </row>
     <row r="229">
@@ -22829,19 +22829,19 @@
         <v>0</v>
       </c>
       <c r="D229" t="n">
-        <v>-0.0740335034467193</v>
+        <v>-0.165116319891259</v>
       </c>
       <c r="E229" t="n">
         <v>-0.197899650539364</v>
       </c>
       <c r="F229" t="n">
-        <v>0.18590347471302</v>
+        <v>0.107630730154888</v>
       </c>
       <c r="G229" t="n">
         <v>0.0204160513133088</v>
       </c>
       <c r="H229" t="n">
-        <v>-0.00296158508503321</v>
+        <v>0.0493861343210963</v>
       </c>
       <c r="I229" t="n">
         <v>-0.053079148925832</v>
@@ -22850,7 +22850,7 @@
         <v>0.0067193024769731</v>
       </c>
       <c r="K229" t="n">
-        <v>-0.119380942769053</v>
+        <v>-0.113637191433968</v>
       </c>
       <c r="L229" t="n">
         <v>0.0113523493807398</v>
@@ -22886,31 +22886,31 @@
         <v>-0.000325851368956437</v>
       </c>
       <c r="W229" t="n">
-        <v>0.0329654654605226</v>
+        <v>0.063561203381111</v>
       </c>
       <c r="X229" t="n">
-        <v>0.0109291482009957</v>
+        <v>0.000018152870251071</v>
       </c>
       <c r="Y229" t="n">
-        <v>-0.133633157475139</v>
+        <v>-0.224715973919679</v>
       </c>
       <c r="Z229" t="n">
         <v>-0.138299996510944</v>
       </c>
       <c r="AA229" t="n">
-        <v>0.157068170398966</v>
+        <v>0.131073674303589</v>
       </c>
       <c r="AB229" t="n">
-        <v>-0.088895039554173</v>
+        <v>-0.0634380142755315</v>
       </c>
       <c r="AC229" t="n">
-        <v>0.0683214224166084</v>
+        <v>0.0677239711369383</v>
       </c>
       <c r="AD229" t="n">
-        <v>-0.203611731569474</v>
+        <v>-0.295291999293684</v>
       </c>
       <c r="AE229" t="n">
-        <v>-0.304625398459499</v>
+        <v>-0.243284718589681</v>
       </c>
     </row>
     <row r="230">
@@ -22924,19 +22924,19 @@
         <v>0</v>
       </c>
       <c r="D230" t="n">
-        <v>-0.156646793912529</v>
+        <v>-0.162254675936471</v>
       </c>
       <c r="E230" t="n">
         <v>-0.20211764350637</v>
       </c>
       <c r="F230" t="n">
-        <v>0.0508575201017416</v>
+        <v>0.0139635545307985</v>
       </c>
       <c r="G230" t="n">
         <v>0.0212613884524714</v>
       </c>
       <c r="H230" t="n">
-        <v>-0.00348616401094434</v>
+        <v>0.0425303234823068</v>
       </c>
       <c r="I230" t="n">
         <v>-0.201670898709106</v>
@@ -22945,7 +22945,7 @@
         <v>0.00826628957641573</v>
       </c>
       <c r="K230" t="n">
-        <v>-0.114471191068539</v>
+        <v>-0.10293882747997</v>
       </c>
       <c r="L230" t="n">
         <v>0.0116439678568133</v>
@@ -22981,31 +22981,31 @@
         <v>-0.000319965038080787</v>
       </c>
       <c r="W230" t="n">
-        <v>0.0339260078475304</v>
+        <v>0.072466915230067</v>
       </c>
       <c r="X230" t="n">
-        <v>0.000739155310379238</v>
+        <v>-0.00628702681993144</v>
       </c>
       <c r="Y230" t="n">
-        <v>-0.202100960212546</v>
+        <v>-0.207708842236488</v>
       </c>
       <c r="Z230" t="n">
         <v>-0.156663477206352</v>
       </c>
       <c r="AA230" t="n">
-        <v>-0.124622310397659</v>
+        <v>-0.115491337879815</v>
       </c>
       <c r="AB230" t="n">
-        <v>-0.0857868419474303</v>
+        <v>-0.042701741532919</v>
       </c>
       <c r="AC230" t="n">
-        <v>-0.210522469371586</v>
+        <v>-0.158245356785274</v>
       </c>
       <c r="AD230" t="n">
-        <v>-0.569286906790484</v>
+        <v>-0.522617676228115</v>
       </c>
       <c r="AE230" t="n">
-        <v>-0.242541307644678</v>
+        <v>-0.229250642076623</v>
       </c>
     </row>
     <row r="231">
@@ -23019,19 +23019,19 @@
         <v>0</v>
       </c>
       <c r="D231" t="n">
-        <v>-6.35462787190733</v>
+        <v>-6.4825650475632</v>
       </c>
       <c r="E231" t="n">
         <v>-10.9180831107143</v>
       </c>
       <c r="F231" t="n">
-        <v>7.24994277935586</v>
+        <v>7.3288722138594</v>
       </c>
       <c r="G231" t="n">
         <v>4.14303025462738</v>
       </c>
       <c r="H231" t="n">
-        <v>0.23620144879535</v>
+        <v>0.229761288016204</v>
       </c>
       <c r="I231" t="n">
         <v>-1.89348158907485</v>
@@ -23040,7 +23040,7 @@
         <v>0.0782687667864247</v>
       </c>
       <c r="K231" t="n">
-        <v>-7.12204386013532</v>
+        <v>-7.11574623799763</v>
       </c>
       <c r="L231" t="n">
         <v>-0.731684035695398</v>
@@ -23076,31 +23076,31 @@
         <v>-0.000252815883905431</v>
       </c>
       <c r="W231" t="n">
-        <v>-5.94385772904819</v>
+        <v>-5.99448737624325</v>
       </c>
       <c r="X231" t="n">
-        <v>-0.975314053476406</v>
+        <v>-0.971539615826814</v>
       </c>
       <c r="Y231" t="n">
-        <v>-7.96055002868393</v>
+        <v>-8.0884872043398</v>
       </c>
       <c r="Z231" t="n">
         <v>-9.31216095393765</v>
       </c>
       <c r="AA231" t="n">
-        <v>9.68228748089152</v>
+        <v>9.75315307695071</v>
       </c>
       <c r="AB231" t="n">
-        <v>-15.6596127135263</v>
+        <v>-15.7038412508325</v>
       </c>
       <c r="AC231" t="n">
-        <v>-4.3735060256683</v>
+        <v>-4.33043574264703</v>
       </c>
       <c r="AD231" t="n">
-        <v>-21.6462170082899</v>
+        <v>-21.7310839009245</v>
       </c>
       <c r="AE231" t="n">
-        <v>-5.66309299133237</v>
+        <v>-5.66872462061369</v>
       </c>
     </row>
     <row r="232">
@@ -23120,13 +23120,13 @@
         <v>#NUM!</v>
       </c>
       <c r="F232" t="n">
-        <v>7.24061874705758</v>
+        <v>7.30017600255913</v>
       </c>
       <c r="G232" t="n">
         <v>4.10363982228423</v>
       </c>
       <c r="H232" t="n">
-        <v>0.231610770995828</v>
+        <v>0.225264301357652</v>
       </c>
       <c r="I232" t="n">
         <v>0</v>
@@ -23135,7 +23135,7 @@
         <v>0.0762012506659499</v>
       </c>
       <c r="K232" t="n">
-        <v>-6.99714711879506</v>
+        <v>-6.99701386962174</v>
       </c>
       <c r="L232" t="n">
         <v>-0.727705117698837</v>
@@ -23171,10 +23171,10 @@
         <v>-0.000247948531799295</v>
       </c>
       <c r="W232" t="n">
-        <v>-5.90258800606652</v>
+        <v>-5.96375327479904</v>
       </c>
       <c r="X232" t="n">
-        <v>-0.965707748995162</v>
+        <v>-0.966809286720248</v>
       </c>
       <c r="Y232" t="e">
         <v>#NUM!</v>
@@ -23183,19 +23183,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA232" t="n">
-        <v>11.2916002369718</v>
+        <v>11.3426905019546</v>
       </c>
       <c r="AB232" t="n">
-        <v>-15.432317162843</v>
+        <v>-15.5002515805719</v>
       </c>
       <c r="AC232" t="n">
-        <v>-2.28876978830089</v>
+        <v>-2.2890309171096</v>
       </c>
       <c r="AD232" t="n">
         <v>0</v>
       </c>
       <c r="AE232" t="n">
-        <v>-5.60477891166246</v>
+        <v>-5.63724839411157</v>
       </c>
     </row>
     <row r="233">
@@ -23215,13 +23215,13 @@
         <v>#NUM!</v>
       </c>
       <c r="F233" t="n">
-        <v>3.70012666585979</v>
+        <v>3.70383543718708</v>
       </c>
       <c r="G233" t="n">
         <v>2.06381297055394</v>
       </c>
       <c r="H233" t="n">
-        <v>0.235503788278021</v>
+        <v>0.229234156125654</v>
       </c>
       <c r="I233" t="n">
         <v>0</v>
@@ -23230,7 +23230,7 @@
         <v>0.0755541209685337</v>
       </c>
       <c r="K233" t="n">
-        <v>-6.88000796891369</v>
+        <v>-6.86747435479228</v>
       </c>
       <c r="L233" t="n">
         <v>-0.725077670364884</v>
@@ -23266,10 +23266,10 @@
         <v>-0.000243588812998019</v>
       </c>
       <c r="W233" t="n">
-        <v>-5.8642497312584</v>
+        <v>-5.90629203205199</v>
       </c>
       <c r="X233" t="n">
-        <v>-0.954076810292782</v>
+        <v>-0.947120950463217</v>
       </c>
       <c r="Y233" t="e">
         <v>#NUM!</v>
@@ -23278,19 +23278,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA233" t="n">
-        <v>5.97363300303747</v>
+        <v>5.9713656487234</v>
       </c>
       <c r="AB233" t="n">
-        <v>-15.232345854173</v>
+        <v>-15.2566839896174</v>
       </c>
       <c r="AC233" t="n">
-        <v>-8.30296838048652</v>
+        <v>-8.32844959134408</v>
       </c>
       <c r="AD233" t="n">
         <v>0</v>
       </c>
       <c r="AE233" t="n">
-        <v>-5.55387597877009</v>
+        <v>-5.56342539428815</v>
       </c>
     </row>
     <row r="234">
@@ -23310,13 +23310,13 @@
         <v>#NUM!</v>
       </c>
       <c r="F234" t="n">
-        <v>3.54124599920147</v>
+        <v>3.6190399799111</v>
       </c>
       <c r="G234" t="n">
         <v>2.04452940303916</v>
       </c>
       <c r="H234" t="n">
-        <v>0.23443383822375</v>
+        <v>0.228250090588388</v>
       </c>
       <c r="I234" t="n">
         <v>0</v>
@@ -23325,7 +23325,7 @@
         <v>0.0785155806756128</v>
       </c>
       <c r="K234" t="n">
-        <v>-6.88177678056897</v>
+        <v>-6.88148463390872</v>
       </c>
       <c r="L234" t="n">
         <v>-0.722042677932606</v>
@@ -23361,10 +23361,10 @@
         <v>-0.000239129527510748</v>
       </c>
       <c r="W234" t="n">
-        <v>-5.82271178477694</v>
+        <v>-5.8832342610377</v>
       </c>
       <c r="X234" t="n">
-        <v>-0.941958385820405</v>
+        <v>-0.943430367024577</v>
       </c>
       <c r="Y234" t="e">
         <v>#NUM!</v>
@@ -23373,19 +23373,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA234" t="n">
-        <v>5.80219913243003</v>
+        <v>5.87220670973692</v>
       </c>
       <c r="AB234" t="n">
-        <v>-15.1625964650592</v>
+        <v>-15.2299649666933</v>
       </c>
       <c r="AC234" t="n">
-        <v>-8.43731193228799</v>
+        <v>-8.41934981094317</v>
       </c>
       <c r="AD234" t="n">
         <v>0</v>
       </c>
       <c r="AE234" t="n">
-        <v>-5.41155425207247</v>
+        <v>-5.43277097523112</v>
       </c>
     </row>
     <row r="235">
@@ -23405,13 +23405,13 @@
         <v>#NUM!</v>
       </c>
       <c r="F235" t="n">
-        <v>3.49547887778444</v>
+        <v>3.57214368642037</v>
       </c>
       <c r="G235" t="n">
         <v>2.02312068909619</v>
       </c>
       <c r="H235" t="n">
-        <v>0.236866424865927</v>
+        <v>0.230756391199535</v>
       </c>
       <c r="I235" t="n">
         <v>0</v>
@@ -23468,19 +23468,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA235" t="n">
-        <v>5.73691017249106</v>
+        <v>5.80589854628874</v>
       </c>
       <c r="AB235" t="n">
         <v>-0.0860268363079363</v>
       </c>
       <c r="AC235" t="n">
-        <v>5.65619406006092</v>
+        <v>5.72524699647437</v>
       </c>
       <c r="AD235" t="n">
         <v>0</v>
       </c>
       <c r="AE235" t="n">
-        <v>0</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="236">
@@ -23500,13 +23500,13 @@
         <v>#NUM!</v>
       </c>
       <c r="F236" t="n">
-        <v>3.45732600778049</v>
+        <v>3.53302887178381</v>
       </c>
       <c r="G236" t="n">
         <v>2.00423722863772</v>
       </c>
       <c r="H236" t="n">
-        <v>0.239850512193163</v>
+        <v>0.0722448881001593</v>
       </c>
       <c r="I236" t="n">
         <v>0</v>
@@ -23563,19 +23563,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA236" t="n">
-        <v>5.68335162943522</v>
+        <v>5.59952103983218</v>
       </c>
       <c r="AB236" t="n">
         <v>-0.0651868979666943</v>
       </c>
       <c r="AC236" t="n">
-        <v>5.62214522412064</v>
+        <v>5.53825530337416</v>
       </c>
       <c r="AD236" t="n">
         <v>0</v>
       </c>
       <c r="AE236" t="n">
-        <v>0</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="237">
@@ -23595,13 +23595,13 @@
         <v>#NUM!</v>
       </c>
       <c r="F237" t="n">
-        <v>3.41595841441796</v>
+        <v>3.49062824628225</v>
       </c>
       <c r="G237" t="n">
         <v>1.98462400626479</v>
       </c>
       <c r="H237" t="n">
-        <v>0.233993888858739</v>
+        <v>0.0705331289343471</v>
       </c>
       <c r="I237" t="n">
         <v>0</v>
@@ -23658,19 +23658,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA237" t="n">
-        <v>5.61736492486516</v>
+        <v>5.53633467011732</v>
       </c>
       <c r="AB237" t="n">
         <v>-0.0649308917620592</v>
       </c>
       <c r="AC237" t="n">
-        <v>5.55635070803114</v>
+        <v>5.47526336804371</v>
       </c>
       <c r="AD237" t="n">
         <v>0</v>
       </c>
       <c r="AE237" t="n">
-        <v>0</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="238">
@@ -23690,13 +23690,13 @@
         <v>#NUM!</v>
       </c>
       <c r="F238" t="n">
-        <v>3.4627109495069</v>
+        <v>3.51824978588587</v>
       </c>
       <c r="G238" t="n">
         <v>1.96748284330751</v>
       </c>
       <c r="H238" t="n">
-        <v>0.228418237905961</v>
+        <v>0.171482084754022</v>
       </c>
       <c r="I238" t="n">
         <v>0</v>
@@ -23753,19 +23753,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA238" t="n">
-        <v>5.64022383642352</v>
+        <v>5.64081814717383</v>
       </c>
       <c r="AB238" t="n">
         <v>-0.0608745265794686</v>
       </c>
       <c r="AC238" t="n">
-        <v>5.58303129663076</v>
+        <v>5.58362599945893</v>
       </c>
       <c r="AD238" t="n">
         <v>0</v>
       </c>
       <c r="AE238" t="n">
-        <v>0</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="239">
@@ -23791,7 +23791,7 @@
         <v>0</v>
       </c>
       <c r="H239" t="n">
-        <v>0.222817251186129</v>
+        <v>0.167276436644511</v>
       </c>
       <c r="I239" t="n">
         <v>0</v>
@@ -23848,19 +23848,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA239" t="n">
-        <v>0.293502538494835</v>
+        <v>0.238003495894634</v>
       </c>
       <c r="AB239" t="n">
         <v>-0.0335228701561467</v>
       </c>
       <c r="AC239" t="n">
-        <v>0.260084071600606</v>
+        <v>0.204565278828774</v>
       </c>
       <c r="AD239" t="n">
         <v>0</v>
       </c>
       <c r="AE239" t="n">
-        <v>0</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="240">
@@ -23886,7 +23886,7 @@
         <v>0</v>
       </c>
       <c r="H240" t="n">
-        <v>0.217095225343289</v>
+        <v>0.162979900079402</v>
       </c>
       <c r="I240" t="n">
         <v>0</v>
@@ -23943,19 +23943,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA240" t="n">
-        <v>0.286316467813129</v>
+        <v>0.232241012889103</v>
       </c>
       <c r="AB240" t="n">
         <v>-0.0327638569113506</v>
       </c>
       <c r="AC240" t="n">
-        <v>0.25365219250096</v>
+        <v>0.199557922250519</v>
       </c>
       <c r="AD240" t="n">
         <v>0</v>
       </c>
       <c r="AE240" t="n">
-        <v>0</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="241">
@@ -23981,7 +23981,7 @@
         <v>0</v>
       </c>
       <c r="H241" t="n">
-        <v>0.211680444347253</v>
+        <v>0.158914143637246</v>
       </c>
       <c r="I241" t="n">
         <v>0</v>
@@ -24038,19 +24038,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA241" t="n">
-        <v>0.279669510502595</v>
+        <v>0.22694137755605</v>
       </c>
       <c r="AB241" t="n">
         <v>-0.0325003623948072</v>
       </c>
       <c r="AC241" t="n">
-        <v>0.247265599956117</v>
+        <v>0.19451927492442</v>
       </c>
       <c r="AD241" t="n">
         <v>0</v>
       </c>
       <c r="AE241" t="n">
-        <v>0</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="242">
@@ -24076,7 +24076,7 @@
         <v>0</v>
       </c>
       <c r="H242" t="n">
-        <v>0.206544383462085</v>
+        <v>0.15953336701643</v>
       </c>
       <c r="I242" t="n">
         <v>0</v>
@@ -24133,19 +24133,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA242" t="n">
-        <v>0.273168337399117</v>
+        <v>0.22619059559475</v>
       </c>
       <c r="AB242" t="n">
         <v>-0.0315912555671793</v>
       </c>
       <c r="AC242" t="n">
-        <v>0.241668531528796</v>
+        <v>0.194675056494781</v>
       </c>
       <c r="AD242" t="n">
         <v>0</v>
       </c>
       <c r="AE242" t="n">
-        <v>0</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="243">
@@ -24240,7 +24240,7 @@
         <v>0</v>
       </c>
       <c r="AE243" t="n">
-        <v>0</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="244">
@@ -24335,7 +24335,7 @@
         <v>0</v>
       </c>
       <c r="AE244" t="n">
-        <v>0</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="245">
@@ -24430,7 +24430,7 @@
         <v>0</v>
       </c>
       <c r="AE245" t="n">
-        <v>0</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="246">
@@ -24525,7 +24525,7 @@
         <v>0</v>
       </c>
       <c r="AE246" t="n">
-        <v>0</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="247">
@@ -24620,7 +24620,7 @@
         <v>0</v>
       </c>
       <c r="AE247" t="n">
-        <v>0</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="248">
@@ -24715,7 +24715,7 @@
         <v>0</v>
       </c>
       <c r="AE248" t="n">
-        <v>0</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="249">
@@ -24810,7 +24810,7 @@
         <v>0</v>
       </c>
       <c r="AE249" t="n">
-        <v>0</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="250">
@@ -24905,7 +24905,7 @@
         <v>0</v>
       </c>
       <c r="AE250" t="n">
-        <v>0</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="251">
@@ -25000,7 +25000,7 @@
         <v>0</v>
       </c>
       <c r="AE251" t="n">
-        <v>0</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="252">
@@ -25095,7 +25095,7 @@
         <v>0</v>
       </c>
       <c r="AE252" t="n">
-        <v>0</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="253">
@@ -25190,7 +25190,7 @@
         <v>0</v>
       </c>
       <c r="AE253" t="n">
-        <v>0</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="254">
@@ -25285,7 +25285,7 @@
         <v>0</v>
       </c>
       <c r="AE254" t="n">
-        <v>0</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="255">
@@ -25380,7 +25380,7 @@
         <v>0</v>
       </c>
       <c r="AE255" t="n">
-        <v>0</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="256">
@@ -25475,7 +25475,7 @@
         <v>0</v>
       </c>
       <c r="AE256" t="n">
-        <v>0</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="257">
@@ -25570,7 +25570,7 @@
         <v>0</v>
       </c>
       <c r="AE257" t="n">
-        <v>0</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="258">
@@ -25665,7 +25665,7 @@
         <v>0</v>
       </c>
       <c r="AE258" t="n">
-        <v>0</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="259">
@@ -25760,7 +25760,7 @@
         <v>0</v>
       </c>
       <c r="AE259" t="n">
-        <v>0</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="260">
@@ -25855,7 +25855,7 @@
         <v>0</v>
       </c>
       <c r="AE260" t="n">
-        <v>0</v>
+        <v>0.000000000000000888178419700125</v>
       </c>
     </row>
   </sheetData>

--- a/results/07-2025/beta/contributions-07-2025.xlsx
+++ b/results/07-2025/beta/contributions-07-2025.xlsx
@@ -776,10 +776,10 @@
     <t xml:space="preserve">2025 Q2</t>
   </si>
   <si>
+    <t xml:space="preserve">2025 Q3</t>
+  </si>
+  <si>
     <t xml:space="preserve">projection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 Q3</t>
   </si>
   <si>
     <t xml:space="preserve">2025 Q4</t>
@@ -22253,189 +22253,189 @@
         <v>253</v>
       </c>
       <c r="B223" t="s">
-        <v>254</v>
+        <v>32</v>
       </c>
       <c r="C223" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D223" t="n">
-        <v>-0.218091441390802</v>
+        <v>-0.391562387656813</v>
       </c>
       <c r="E223" t="n">
-        <v>-0.199879916241108</v>
+        <v>0.0781528904100504</v>
       </c>
       <c r="F223" t="n">
-        <v>-0.193755484006591</v>
+        <v>-0.423915636094668</v>
       </c>
       <c r="G223" t="n">
-        <v>-0.0559619450645807</v>
+        <v>-0.0589586562014646</v>
       </c>
       <c r="H223" t="n">
-        <v>-0.0301013843879923</v>
+        <v>0.217536719389177</v>
       </c>
       <c r="I223" t="n">
-        <v>0.18892173770625</v>
+        <v>0.186318851219056</v>
       </c>
       <c r="J223" t="n">
-        <v>0.00224347704566236</v>
+        <v>0.0817396190303596</v>
       </c>
       <c r="K223" t="n">
-        <v>0.145933257747981</v>
+        <v>0.374980570389029</v>
       </c>
       <c r="L223" t="n">
-        <v>0.0327070399861267</v>
+        <v>-0.00852330729001726</v>
       </c>
       <c r="M223" t="n">
         <v>0</v>
       </c>
       <c r="N223" t="n">
-        <v>-0.0951822173211808</v>
+        <v>-0.0944410633449994</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
       </c>
       <c r="P223" t="n">
-        <v>-0.00161616513169965</v>
+        <v>0.0007240886257028</v>
       </c>
       <c r="Q223" t="n">
-        <v>-0.107346852927363</v>
+        <v>-0.0939392772317754</v>
       </c>
       <c r="R223" t="n">
-        <v>-0.0267634483508147</v>
+        <v>-0.0265892738036949</v>
       </c>
       <c r="S223" t="n">
-        <v>-0.0134430756420774</v>
+        <v>-0.0134023793177287</v>
       </c>
       <c r="T223" t="n">
-        <v>-0.00999928911444191</v>
+        <v>-0.00996159982828873</v>
       </c>
       <c r="U223" t="n">
-        <v>-0.0237626503078603</v>
+        <v>-0.0236069317052464</v>
       </c>
       <c r="V223" t="n">
-        <v>-0.00151505975298941</v>
+        <v>-0.00103193276551185</v>
       </c>
       <c r="W223" t="n">
-        <v>0.242347826012976</v>
+        <v>0.281367873778438</v>
       </c>
       <c r="X223" t="n">
-        <v>-0.00677250107663066</v>
+        <v>-0.021653933348015</v>
       </c>
       <c r="Y223" t="n">
-        <v>-0.420856160364451</v>
+        <v>-0.831205203287137</v>
       </c>
       <c r="Z223" t="n">
-        <v>0.00288480273254083</v>
+        <v>0.517795706040374</v>
       </c>
       <c r="AA223" t="n">
-        <v>-0.088289444952879</v>
+        <v>0.00416006564299416</v>
       </c>
       <c r="AB223" t="n">
-        <v>0.135033221417888</v>
+        <v>0.364490028612786</v>
       </c>
       <c r="AC223" t="n">
-        <v>-0.953131244205811</v>
+        <v>0.0686340024175949</v>
       </c>
       <c r="AD223" t="n">
-        <v>-1.37110260183772</v>
+        <v>-0.244775494829168</v>
       </c>
       <c r="AE223" t="n">
-        <v>-0.257772291758256</v>
+        <v>0.0238094849938818</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="s">
+        <v>254</v>
+      </c>
+      <c r="B224" t="s">
         <v>255</v>
       </c>
-      <c r="B224" t="s">
-        <v>254</v>
-      </c>
       <c r="C224" t="n">
         <v>0</v>
       </c>
       <c r="D224" t="n">
-        <v>-0.166335102426299</v>
+        <v>0.0291015472775402</v>
       </c>
       <c r="E224" t="n">
-        <v>-0.188402753588166</v>
+        <v>-0.188207035970589</v>
       </c>
       <c r="F224" t="n">
-        <v>-0.0412561055214425</v>
+        <v>-0.28448146421088</v>
       </c>
       <c r="G224" t="n">
-        <v>-0.00499532512598115</v>
+        <v>-0.0246809389958226</v>
       </c>
       <c r="H224" t="n">
-        <v>0.141866401137088</v>
+        <v>0.145262780558903</v>
       </c>
       <c r="I224" t="n">
-        <v>0.185730312532247</v>
+        <v>0.185359698888098</v>
       </c>
       <c r="J224" t="n">
-        <v>0.00443244239695823</v>
+        <v>0.00351457865919616</v>
       </c>
       <c r="K224" t="n">
-        <v>0.0622464797845458</v>
+        <v>0.314442373113224</v>
       </c>
       <c r="L224" t="n">
-        <v>0.00852043015136036</v>
+        <v>0.00894725752390453</v>
       </c>
       <c r="M224" t="n">
         <v>0</v>
       </c>
       <c r="N224" t="n">
-        <v>-0.00100016502131545</v>
+        <v>-0.000998172134519155</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
       </c>
       <c r="P224" t="n">
-        <v>-0.0041718386997037</v>
+        <v>-0.00460271895022645</v>
       </c>
       <c r="Q224" t="n">
-        <v>-0.0848962106379414</v>
+        <v>-0.0729284242867051</v>
       </c>
       <c r="R224" t="n">
-        <v>-0.0261573057546611</v>
+        <v>-0.0261051959502162</v>
       </c>
       <c r="S224" t="n">
-        <v>-0.0137688622776875</v>
+        <v>-0.0137414297319154</v>
       </c>
       <c r="T224" t="n">
-        <v>-0.00851524956552311</v>
+        <v>-0.00849828342381878</v>
       </c>
       <c r="U224" t="n">
-        <v>0.000164989033884506</v>
+        <v>-0.0297244343570672</v>
       </c>
       <c r="V224" t="n">
-        <v>-0.000451773171946533</v>
+        <v>-0.000520541582908059</v>
       </c>
       <c r="W224" t="n">
-        <v>0.170312754424817</v>
+        <v>0.2121781891664</v>
       </c>
       <c r="X224" t="n">
-        <v>0.0157297326996495</v>
+        <v>0.0232516749060726</v>
       </c>
       <c r="Y224" t="n">
-        <v>-0.219460421715788</v>
+        <v>-0.0229827206853852</v>
       </c>
       <c r="Z224" t="n">
-        <v>-0.135277434298677</v>
+        <v>-0.136122768007664</v>
       </c>
       <c r="AA224" t="n">
-        <v>0.285644148739794</v>
+        <v>0.0256963569760872</v>
       </c>
       <c r="AB224" t="n">
-        <v>0.118157605258083</v>
+        <v>0.401648149945798</v>
       </c>
       <c r="AC224" t="n">
-        <v>-0.596554324326954</v>
+        <v>0.127235077838726</v>
       </c>
       <c r="AD224" t="n">
-        <v>-0.951292180341419</v>
+        <v>-0.031870410854323</v>
       </c>
       <c r="AE224" t="n">
-        <v>-0.620953349356321</v>
+        <v>-0.109516130232409</v>
       </c>
     </row>
     <row r="225">
@@ -22443,94 +22443,94 @@
         <v>256</v>
       </c>
       <c r="B225" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C225" t="n">
         <v>0</v>
       </c>
       <c r="D225" t="n">
-        <v>0.138347808668163</v>
+        <v>-0.147415260686794</v>
       </c>
       <c r="E225" t="n">
-        <v>-0.187426688324483</v>
+        <v>-0.187231984668563</v>
       </c>
       <c r="F225" t="n">
-        <v>-0.00571382019883403</v>
+        <v>-0.193197673751037</v>
       </c>
       <c r="G225" t="n">
-        <v>-0.0153552438046491</v>
+        <v>-0.0138590061138467</v>
       </c>
       <c r="H225" t="n">
-        <v>0.140377254322351</v>
+        <v>0.0307276148291852</v>
       </c>
       <c r="I225" t="n">
-        <v>0.0729643688673298</v>
+        <v>0.0721388183794355</v>
       </c>
       <c r="J225" t="n">
-        <v>0.00545401864232233</v>
+        <v>0.00498265591511215</v>
       </c>
       <c r="K225" t="n">
-        <v>-0.0366943534705917</v>
+        <v>0.22585716259006</v>
       </c>
       <c r="L225" t="n">
-        <v>0.0314648671659881</v>
+        <v>0.0305012797511961</v>
       </c>
       <c r="M225" t="n">
         <v>0</v>
       </c>
       <c r="N225" t="n">
-        <v>-0.000976949995653429</v>
+        <v>-0.000975940925236092</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
       </c>
       <c r="P225" t="n">
-        <v>-0.00489661380609627</v>
+        <v>-0.00526220081185437</v>
       </c>
       <c r="Q225" t="n">
-        <v>-0.0462332530519806</v>
+        <v>-0.0356074781047652</v>
       </c>
       <c r="R225" t="n">
-        <v>-0.00391905108893008</v>
+        <v>-0.00391689079893773</v>
       </c>
       <c r="S225" t="n">
-        <v>-0.012892032829348</v>
+        <v>-0.0128933818456295</v>
       </c>
       <c r="T225" t="n">
-        <v>-0.00769583359513529</v>
+        <v>-0.0076975622841696</v>
       </c>
       <c r="U225" t="n">
-        <v>0.00012031268635897</v>
+        <v>-0.0246723690474352</v>
       </c>
       <c r="V225" t="n">
-        <v>-0.000419227109622843</v>
+        <v>-0.000445890310880037</v>
       </c>
       <c r="W225" t="n">
-        <v>0.129494712030853</v>
+        <v>0.15990612829068</v>
       </c>
       <c r="X225" t="n">
-        <v>0.0374417781397447</v>
+        <v>0.0405795583280417</v>
       </c>
       <c r="Y225" t="n">
-        <v>0.0328023769392936</v>
+        <v>-0.251753485381384</v>
       </c>
       <c r="Z225" t="n">
-        <v>-0.0818812565956142</v>
+        <v>-0.0828937599739729</v>
       </c>
       <c r="AA225" t="n">
-        <v>0.197653824473987</v>
+        <v>-0.0990280287837447</v>
       </c>
       <c r="AB225" t="n">
-        <v>0.0848773632426025</v>
+        <v>0.365095059937961</v>
       </c>
       <c r="AC225" t="n">
-        <v>-0.717646085911434</v>
+        <v>-0.0335490520877683</v>
       </c>
       <c r="AD225" t="n">
-        <v>-0.766724965567754</v>
+        <v>-0.368196297443125</v>
       </c>
       <c r="AE225" t="n">
-        <v>-0.900557906729174</v>
+        <v>-0.289488520574104</v>
       </c>
     </row>
     <row r="226">
@@ -22538,94 +22538,94 @@
         <v>257</v>
       </c>
       <c r="B226" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C226" t="n">
         <v>0</v>
       </c>
       <c r="D226" t="n">
-        <v>0.182123494913557</v>
+        <v>0.18276212819498</v>
       </c>
       <c r="E226" t="n">
-        <v>-0.186244865759511</v>
+        <v>-0.186051389811214</v>
       </c>
       <c r="F226" t="n">
-        <v>0.141087528212335</v>
+        <v>-0.124853598459061</v>
       </c>
       <c r="G226" t="n">
-        <v>-0.0206587577015947</v>
+        <v>-0.0302352091264087</v>
       </c>
       <c r="H226" t="n">
-        <v>0.0352176317081096</v>
+        <v>0.0420773171393092</v>
       </c>
       <c r="I226" t="n">
-        <v>0.316467212868588</v>
+        <v>0.315835073308651</v>
       </c>
       <c r="J226" t="n">
-        <v>0.00364314963120222</v>
+        <v>0.00279733949862842</v>
       </c>
       <c r="K226" t="n">
-        <v>-0.175460839059818</v>
+        <v>0.119957971224332</v>
       </c>
       <c r="L226" t="n">
-        <v>0.0385868919646275</v>
+        <v>0.0389192434923418</v>
       </c>
       <c r="M226" t="n">
         <v>0</v>
       </c>
       <c r="N226" t="n">
-        <v>-0.000954336745202481</v>
+        <v>-0.000952435173347631</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
       </c>
       <c r="P226" t="n">
-        <v>-0.00451074768276966</v>
+        <v>-0.00465781480912921</v>
       </c>
       <c r="Q226" t="n">
-        <v>-0.0140047312892732</v>
+        <v>-0.00397491792910585</v>
       </c>
       <c r="R226" t="n">
-        <v>-0.00268474876865709</v>
+        <v>-0.00267939932142978</v>
       </c>
       <c r="S226" t="n">
-        <v>-0.0143859668434188</v>
+        <v>-0.0143573049569729</v>
       </c>
       <c r="T226" t="n">
-        <v>-0.00708518717718778</v>
+        <v>-0.00707107020008399</v>
       </c>
       <c r="U226" t="n">
-        <v>-0.000164736377340404</v>
+        <v>-0.0229254872932519</v>
       </c>
       <c r="V226" t="n">
-        <v>-0.000388464898983852</v>
+        <v>-0.00041272833968232</v>
       </c>
       <c r="W226" t="n">
-        <v>0.135514231959327</v>
+        <v>0.176361284115549</v>
       </c>
       <c r="X226" t="n">
-        <v>-0.00480605503782594</v>
+        <v>-0.00263935170918194</v>
       </c>
       <c r="Y226" t="n">
-        <v>0.129587536159072</v>
+        <v>0.131365421185271</v>
       </c>
       <c r="Z226" t="n">
-        <v>-0.133708907005026</v>
+        <v>-0.134654682801505</v>
       </c>
       <c r="AA226" t="n">
-        <v>0.475201884951763</v>
+        <v>0.206024476956956</v>
       </c>
       <c r="AB226" t="n">
-        <v>-0.0500870100151668</v>
+        <v>0.275418168268284</v>
       </c>
       <c r="AC226" t="n">
-        <v>-0.574632611434394</v>
+        <v>0.18083761874536</v>
       </c>
       <c r="AD226" t="n">
-        <v>-0.578753982280349</v>
+        <v>0.177548357129126</v>
       </c>
       <c r="AE226" t="n">
-        <v>-0.916968432506811</v>
+        <v>-0.116823461499373</v>
       </c>
     </row>
     <row r="227">
@@ -22633,37 +22633,37 @@
         <v>258</v>
       </c>
       <c r="B227" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C227" t="n">
         <v>0</v>
       </c>
       <c r="D227" t="n">
-        <v>-0.091179211129241</v>
+        <v>-0.0914989396674436</v>
       </c>
       <c r="E227" t="n">
-        <v>-0.197303734077729</v>
+        <v>-0.197098769893092</v>
       </c>
       <c r="F227" t="n">
-        <v>0.114356039802799</v>
+        <v>-0.111831377165716</v>
       </c>
       <c r="G227" t="n">
-        <v>-0.00901379205779021</v>
+        <v>-0.0185363518653894</v>
       </c>
       <c r="H227" t="n">
-        <v>0.0330798926987005</v>
+        <v>0.0397911929794883</v>
       </c>
       <c r="I227" t="n">
-        <v>0.251039235479208</v>
+        <v>0.250538044168492</v>
       </c>
       <c r="J227" t="n">
-        <v>0.00487621229521312</v>
+        <v>0.00405859116102814</v>
       </c>
       <c r="K227" t="n">
-        <v>-0.168986483119721</v>
+        <v>-0.0964496209567767</v>
       </c>
       <c r="L227" t="n">
-        <v>0.0110356741019841</v>
+        <v>0.0483076284777866</v>
       </c>
       <c r="M227" t="n">
         <v>0</v>
@@ -22675,52 +22675,52 @@
         <v>0</v>
       </c>
       <c r="P227" t="n">
-        <v>-0.00420973231703228</v>
+        <v>-0.00501229776042769</v>
       </c>
       <c r="Q227" t="n">
-        <v>-0.00989933319121142</v>
+        <v>-0.00123929059572625</v>
       </c>
       <c r="R227" t="n">
-        <v>-0.00225461695578231</v>
+        <v>-0.00225012454482906</v>
       </c>
       <c r="S227" t="n">
-        <v>-0.0098984505432875</v>
+        <v>-0.00987872867142038</v>
       </c>
       <c r="T227" t="n">
-        <v>-0.00650647343661458</v>
+        <v>-0.00649350946650114</v>
       </c>
       <c r="U227" t="n">
-        <v>-0.000193243594692404</v>
+        <v>-0.0210948866777623</v>
       </c>
       <c r="V227" t="n">
-        <v>-0.000339139413338695</v>
+        <v>-0.000383695634204903</v>
       </c>
       <c r="W227" t="n">
-        <v>0.0952519114350495</v>
+        <v>0.0759890946654891</v>
       </c>
       <c r="X227" t="n">
-        <v>0.0168723614178661</v>
+        <v>0.0281761613382162</v>
       </c>
       <c r="Y227" t="n">
-        <v>-0.176474611396261</v>
+        <v>-0.175711028259567</v>
       </c>
       <c r="Z227" t="n">
-        <v>-0.11200833381071</v>
+        <v>-0.112886681300968</v>
       </c>
       <c r="AA227" t="n">
-        <v>0.393923358464019</v>
+        <v>0.164287776318198</v>
       </c>
       <c r="AB227" t="n">
-        <v>-0.0789579260105366</v>
+        <v>0.00977034355799154</v>
       </c>
       <c r="AC227" t="n">
-        <v>0.315294958430772</v>
+        <v>-0.0259589655707904</v>
       </c>
       <c r="AD227" t="n">
-        <v>0.0268120132238019</v>
+        <v>-0.314556675131326</v>
       </c>
       <c r="AE227" t="n">
-        <v>-0.56748977874143</v>
+        <v>-0.134268756574912</v>
       </c>
     </row>
     <row r="228">
@@ -22728,37 +22728,37 @@
         <v>259</v>
       </c>
       <c r="B228" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C228" t="n">
         <v>0</v>
       </c>
       <c r="D228" t="n">
-        <v>-0.0711419432935427</v>
+        <v>-0.0713914092546146</v>
       </c>
       <c r="E228" t="n">
-        <v>-0.187119724943941</v>
+        <v>-0.186925340169462</v>
       </c>
       <c r="F228" t="n">
-        <v>0.0724111854320921</v>
+        <v>-0.133711890385013</v>
       </c>
       <c r="G228" t="n">
-        <v>0.00509242029859333</v>
+        <v>-0.0043181761913685</v>
       </c>
       <c r="H228" t="n">
-        <v>0.0432668687960049</v>
+        <v>0.0497382359617767</v>
       </c>
       <c r="I228" t="n">
-        <v>0.0775952242339403</v>
+        <v>0.0774405162859638</v>
       </c>
       <c r="J228" t="n">
-        <v>0.00640109336423803</v>
+        <v>0.00559558692157512</v>
       </c>
       <c r="K228" t="n">
-        <v>-0.163478264136423</v>
+        <v>-0.066201433696298</v>
       </c>
       <c r="L228" t="n">
-        <v>0.0112179112527027</v>
+        <v>0.0111955567825106</v>
       </c>
       <c r="M228" t="n">
         <v>0</v>
@@ -22770,52 +22770,52 @@
         <v>0</v>
       </c>
       <c r="P228" t="n">
-        <v>-0.00454918909062775</v>
+        <v>-0.00507216806458537</v>
       </c>
       <c r="Q228" t="n">
-        <v>-0.0088581224085032</v>
+        <v>-0.000459949846609852</v>
       </c>
       <c r="R228" t="n">
-        <v>-0.00284512609217039</v>
+        <v>-0.00283945709569163</v>
       </c>
       <c r="S228" t="n">
-        <v>-0.0067501660679194</v>
+        <v>-0.00673671657610257</v>
       </c>
       <c r="T228" t="n">
-        <v>-0.00580387405377487</v>
+        <v>-0.0057923099332822</v>
       </c>
       <c r="U228" t="n">
-        <v>-0.00731357373464781</v>
+        <v>-0.0191280140611447</v>
       </c>
       <c r="V228" t="n">
-        <v>-0.000331243183112972</v>
+        <v>-0.000333844436854403</v>
       </c>
       <c r="W228" t="n">
-        <v>0.0973185863976518</v>
+        <v>0.0910284558715304</v>
       </c>
       <c r="X228" t="n">
-        <v>0.018809714516209</v>
+        <v>0.0142159535339324</v>
       </c>
       <c r="Y228" t="n">
-        <v>-0.105730073570082</v>
+        <v>-0.105034412883283</v>
       </c>
       <c r="Z228" t="n">
-        <v>-0.152531594667403</v>
+        <v>-0.153282336540794</v>
       </c>
       <c r="AA228" t="n">
-        <v>0.204613883045715</v>
+        <v>-0.00511473222964723</v>
       </c>
       <c r="AB228" t="n">
-        <v>-0.0724148963587344</v>
+        <v>0.00994764383847354</v>
       </c>
       <c r="AC228" t="n">
-        <v>0.132356762228991</v>
+        <v>-0.195166544065889</v>
       </c>
       <c r="AD228" t="n">
-        <v>-0.125904906008493</v>
+        <v>-0.453483293489966</v>
       </c>
       <c r="AE228" t="n">
-        <v>-0.361142960158199</v>
+        <v>-0.239671977233823</v>
       </c>
     </row>
     <row r="229">
@@ -22823,37 +22823,37 @@
         <v>260</v>
       </c>
       <c r="B229" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C229" t="n">
         <v>0</v>
       </c>
       <c r="D229" t="n">
-        <v>-0.165116319891259</v>
+        <v>-0.165695315902942</v>
       </c>
       <c r="E229" t="n">
-        <v>-0.197899650539364</v>
+        <v>-0.197694067301406</v>
       </c>
       <c r="F229" t="n">
-        <v>0.107630730154888</v>
+        <v>-0.101365325995295</v>
       </c>
       <c r="G229" t="n">
-        <v>0.0204160513133088</v>
+        <v>0.0110463487191915</v>
       </c>
       <c r="H229" t="n">
-        <v>0.0493861343210963</v>
+        <v>0.055669138497308</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.053079148925832</v>
+        <v>-0.052973428563513</v>
       </c>
       <c r="J229" t="n">
-        <v>0.0067193024769731</v>
+        <v>0.00591935690801142</v>
       </c>
       <c r="K229" t="n">
-        <v>-0.113637191433968</v>
+        <v>-0.0180679238248527</v>
       </c>
       <c r="L229" t="n">
-        <v>0.0113523493807398</v>
+        <v>0.0113297269904241</v>
       </c>
       <c r="M229" t="n">
         <v>0</v>
@@ -22865,52 +22865,52 @@
         <v>0</v>
       </c>
       <c r="P229" t="n">
-        <v>-0.00468131002505322</v>
+        <v>-0.00467883109052618</v>
       </c>
       <c r="Q229" t="n">
-        <v>-0.00700452739965782</v>
+        <v>0.0012426761551968</v>
       </c>
       <c r="R229" t="n">
-        <v>-0.000299415556678647</v>
+        <v>-0.000298818950572954</v>
       </c>
       <c r="S229" t="n">
-        <v>-0.00308423277811088</v>
+        <v>-0.00307808736574553</v>
       </c>
       <c r="T229" t="n">
-        <v>-0.00322608397678872</v>
+        <v>-0.00321965592940295</v>
       </c>
       <c r="U229" t="n">
-        <v>-0.00618108553229408</v>
+        <v>-0.0121080149151937</v>
       </c>
       <c r="V229" t="n">
-        <v>-0.000325851368956437</v>
+        <v>-0.000328437891201737</v>
       </c>
       <c r="W229" t="n">
-        <v>0.063561203381111</v>
+        <v>0.0574548369395306</v>
       </c>
       <c r="X229" t="n">
-        <v>0.000018152870251071</v>
+        <v>-0.00183318436536394</v>
       </c>
       <c r="Y229" t="n">
-        <v>-0.224715973919679</v>
+        <v>-0.224309758947194</v>
       </c>
       <c r="Z229" t="n">
-        <v>-0.138299996510944</v>
+        <v>-0.139079624257154</v>
       </c>
       <c r="AA229" t="n">
-        <v>0.131073674303589</v>
+        <v>-0.0816523327738605</v>
       </c>
       <c r="AB229" t="n">
-        <v>-0.0634380142755315</v>
+        <v>0.0264316382478804</v>
       </c>
       <c r="AC229" t="n">
-        <v>0.0677239711369383</v>
+        <v>-0.255197664986214</v>
       </c>
       <c r="AD229" t="n">
-        <v>-0.295291999293684</v>
+        <v>-0.618587048190562</v>
       </c>
       <c r="AE229" t="n">
-        <v>-0.243284718589681</v>
+        <v>-0.302269664920682</v>
       </c>
     </row>
     <row r="230">
@@ -22918,37 +22918,37 @@
         <v>261</v>
       </c>
       <c r="B230" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C230" t="n">
         <v>0</v>
       </c>
       <c r="D230" t="n">
-        <v>-0.162254675936471</v>
+        <v>-0.162823637322638</v>
       </c>
       <c r="E230" t="n">
-        <v>-0.20211764350637</v>
+        <v>-0.201907678509023</v>
       </c>
       <c r="F230" t="n">
-        <v>0.0139635545307985</v>
+        <v>-0.208494405668798</v>
       </c>
       <c r="G230" t="n">
-        <v>0.0212613884524714</v>
+        <v>0.0119546139133029</v>
       </c>
       <c r="H230" t="n">
-        <v>0.0425303234823068</v>
+        <v>0.0493810541992499</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.201670898709106</v>
+        <v>-0.20126968450116</v>
       </c>
       <c r="J230" t="n">
-        <v>0.00826628957641573</v>
+        <v>0.00747498910597346</v>
       </c>
       <c r="K230" t="n">
-        <v>-0.10293882747997</v>
+        <v>-0.00974549636439345</v>
       </c>
       <c r="L230" t="n">
-        <v>0.0116439678568133</v>
+        <v>0.0116207642944175</v>
       </c>
       <c r="M230" t="n">
         <v>0</v>
@@ -22960,52 +22960,52 @@
         <v>0</v>
       </c>
       <c r="P230" t="n">
-        <v>-0.00187764733923033</v>
+        <v>-0.00200871387649046</v>
       </c>
       <c r="Q230" t="n">
-        <v>-0.00623589218857423</v>
+        <v>0.00185701407274331</v>
       </c>
       <c r="R230" t="n">
-        <v>-0.000293941335302597</v>
+        <v>-0.000293355636933606</v>
       </c>
       <c r="S230" t="n">
-        <v>-0.0013770967366819</v>
+        <v>-0.00137435279977466</v>
       </c>
       <c r="T230" t="n">
-        <v>-0.00182418112185561</v>
+        <v>-0.00182054635875799</v>
       </c>
       <c r="U230" t="n">
-        <v>-0.0057337276081452</v>
+        <v>-0.0115490525077617</v>
       </c>
       <c r="V230" t="n">
-        <v>-0.000319965038080787</v>
+        <v>-0.000322515093892632</v>
       </c>
       <c r="W230" t="n">
-        <v>0.072466915230067</v>
+        <v>0.0663193428782925</v>
       </c>
       <c r="X230" t="n">
-        <v>-0.00628702681993144</v>
+        <v>-0.00524459066796074</v>
       </c>
       <c r="Y230" t="n">
-        <v>-0.207708842236488</v>
+        <v>-0.207360846589146</v>
       </c>
       <c r="Z230" t="n">
-        <v>-0.156663477206352</v>
+        <v>-0.157370469242515</v>
       </c>
       <c r="AA230" t="n">
-        <v>-0.115491337879815</v>
+        <v>-0.341110887762956</v>
       </c>
       <c r="AB230" t="n">
-        <v>-0.042701741532919</v>
+        <v>0.0474520937058321</v>
       </c>
       <c r="AC230" t="n">
-        <v>-0.158245356785274</v>
+        <v>-0.39348640801367</v>
       </c>
       <c r="AD230" t="n">
-        <v>-0.522617676228115</v>
+        <v>-0.75821772384533</v>
       </c>
       <c r="AE230" t="n">
-        <v>-0.229250642076623</v>
+        <v>-0.536211185164296</v>
       </c>
     </row>
     <row r="231">
@@ -23013,37 +23013,37 @@
         <v>262</v>
       </c>
       <c r="B231" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C231" t="n">
         <v>0</v>
       </c>
       <c r="D231" t="n">
-        <v>-6.4825650475632</v>
+        <v>-0.140907683756577</v>
       </c>
       <c r="E231" t="n">
-        <v>-10.9180831107143</v>
+        <v>-0.190425237576237</v>
       </c>
       <c r="F231" t="n">
-        <v>7.3288722138594</v>
+        <v>-0.0449755394677347</v>
       </c>
       <c r="G231" t="n">
-        <v>4.14303025462738</v>
+        <v>0.0200104973840823</v>
       </c>
       <c r="H231" t="n">
-        <v>0.229761288016204</v>
+        <v>0.0634489810496287</v>
       </c>
       <c r="I231" t="n">
-        <v>-1.89348158907485</v>
+        <v>-0.3127409257165</v>
       </c>
       <c r="J231" t="n">
-        <v>0.0782687667864247</v>
+        <v>0.00490226587861304</v>
       </c>
       <c r="K231" t="n">
-        <v>-7.11574623799763</v>
+        <v>-0.00539983987231659</v>
       </c>
       <c r="L231" t="n">
-        <v>-0.731684035695398</v>
+        <v>0.0118544741668678</v>
       </c>
       <c r="M231" t="n">
         <v>0</v>
@@ -23055,52 +23055,52 @@
         <v>0</v>
       </c>
       <c r="P231" t="n">
-        <v>-0.0952216158720243</v>
+        <v>-0.000156500953837483</v>
       </c>
       <c r="Q231" t="n">
-        <v>-0.0669447453001275</v>
+        <v>0.00150745580400287</v>
       </c>
       <c r="R231" t="n">
-        <v>-0.000287184237423035</v>
+        <v>-0.000286612003097306</v>
       </c>
       <c r="S231" t="n">
-        <v>-0.00103938714852706</v>
+        <v>-0.00103731611021143</v>
       </c>
       <c r="T231" t="n">
-        <v>-0.00153416774184709</v>
+        <v>-0.0015311108367649</v>
       </c>
       <c r="U231" t="n">
-        <v>-0.00527371566857916</v>
+        <v>-0.00956113583778143</v>
       </c>
       <c r="V231" t="n">
-        <v>-0.000252815883905431</v>
+        <v>-0.000315181928034319</v>
       </c>
       <c r="W231" t="n">
-        <v>-5.99448737624325</v>
+        <v>0.0639814185095286</v>
       </c>
       <c r="X231" t="n">
-        <v>-0.971539615826814</v>
+        <v>0.00223218222181615</v>
       </c>
       <c r="Y231" t="n">
-        <v>-8.0884872043398</v>
+        <v>-0.184532529701216</v>
       </c>
       <c r="Z231" t="n">
-        <v>-9.31216095393765</v>
+        <v>-0.146800391631598</v>
       </c>
       <c r="AA231" t="n">
-        <v>9.75315307695071</v>
+        <v>-0.269184928564189</v>
       </c>
       <c r="AB231" t="n">
-        <v>-15.7038412508325</v>
+        <v>0.0612910936078365</v>
       </c>
       <c r="AC231" t="n">
-        <v>-4.33043574264703</v>
+        <v>-0.307717320548898</v>
       </c>
       <c r="AD231" t="n">
-        <v>-21.7310839009245</v>
+        <v>-0.639050241881713</v>
       </c>
       <c r="AE231" t="n">
-        <v>-5.66872462061369</v>
+        <v>-0.617334576851893</v>
       </c>
     </row>
     <row r="232">
@@ -23108,37 +23108,37 @@
         <v>263</v>
       </c>
       <c r="B232" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C232" t="n">
         <v>0</v>
       </c>
-      <c r="D232" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="E232" t="e">
-        <v>#NUM!</v>
+      <c r="D232" t="n">
+        <v>-6.48061066878841</v>
+      </c>
+      <c r="E232" t="n">
+        <v>-10.8986278041055</v>
       </c>
       <c r="F232" t="n">
-        <v>7.30017600255913</v>
+        <v>7.67762368726203</v>
       </c>
       <c r="G232" t="n">
-        <v>4.10363982228423</v>
+        <v>4.15575500555642</v>
       </c>
       <c r="H232" t="n">
-        <v>0.225264301357652</v>
+        <v>0.224742111822221</v>
       </c>
       <c r="I232" t="n">
-        <v>0</v>
+        <v>-1.57354468312711</v>
       </c>
       <c r="J232" t="n">
-        <v>0.0762012506659499</v>
+        <v>0.0760479325580349</v>
       </c>
       <c r="K232" t="n">
-        <v>-6.99701386962174</v>
+        <v>-7.44272261744311</v>
       </c>
       <c r="L232" t="n">
-        <v>-0.727705117698837</v>
+        <v>-0.733943783378817</v>
       </c>
       <c r="M232" t="n">
         <v>0</v>
@@ -23150,52 +23150,52 @@
         <v>0</v>
       </c>
       <c r="P232" t="n">
-        <v>-0.0796761329350507</v>
+        <v>-0.0946835715297874</v>
       </c>
       <c r="Q232" t="n">
-        <v>-0.0571455986269759</v>
+        <v>-0.0727083619463073</v>
       </c>
       <c r="R232" t="n">
-        <v>-0.00028154703118359</v>
+        <v>-0.000280986029323721</v>
       </c>
       <c r="S232" t="n">
-        <v>-0.00102343496699277</v>
+        <v>-0.00102139571406392</v>
       </c>
       <c r="T232" t="n">
-        <v>-0.00126813674339301</v>
+        <v>-0.00126560991298953</v>
       </c>
       <c r="U232" t="n">
-        <v>-0.00313943038300912</v>
+        <v>0.0257296506286633</v>
       </c>
       <c r="V232" t="n">
-        <v>-0.000247948531799295</v>
+        <v>-0.000249918093292196</v>
       </c>
       <c r="W232" t="n">
-        <v>-5.96375327479904</v>
+        <v>-6.0560894156482</v>
       </c>
       <c r="X232" t="n">
-        <v>-0.966809286720248</v>
-      </c>
-      <c r="Y232" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="Z232" t="e">
-        <v>#NUM!</v>
+        <v>-0.977688018024556</v>
+      </c>
+      <c r="Y232" t="n">
+        <v>-8.01277043535423</v>
+      </c>
+      <c r="Z232" t="n">
+        <v>-9.36646803753971</v>
       </c>
       <c r="AA232" t="n">
-        <v>11.3426905019546</v>
+        <v>10.3752838690418</v>
       </c>
       <c r="AB232" t="n">
-        <v>-15.5002515805719</v>
+        <v>-16.1088882869701</v>
       </c>
       <c r="AC232" t="n">
-        <v>-2.2890309171096</v>
+        <v>-3.95381115939138</v>
       </c>
       <c r="AD232" t="n">
-        <v>0</v>
+        <v>-21.3330496322853</v>
       </c>
       <c r="AE232" t="n">
-        <v>-5.63724839411157</v>
+        <v>-5.83722616155073</v>
       </c>
     </row>
     <row r="233">
@@ -23203,7 +23203,7 @@
         <v>264</v>
       </c>
       <c r="B233" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C233" t="n">
         <v>0</v>
@@ -23215,25 +23215,25 @@
         <v>#NUM!</v>
       </c>
       <c r="F233" t="n">
-        <v>3.70383543718708</v>
+        <v>7.62915874462344</v>
       </c>
       <c r="G233" t="n">
-        <v>2.06381297055394</v>
+        <v>4.12139391083715</v>
       </c>
       <c r="H233" t="n">
-        <v>0.229234156125654</v>
+        <v>0.228704907457406</v>
       </c>
       <c r="I233" t="n">
         <v>0</v>
       </c>
       <c r="J233" t="n">
-        <v>0.0755541209685337</v>
+        <v>0.0754021107266993</v>
       </c>
       <c r="K233" t="n">
-        <v>-6.86747435479228</v>
+        <v>-7.33428990531396</v>
       </c>
       <c r="L233" t="n">
-        <v>-0.725077670364884</v>
+        <v>-0.731228528033425</v>
       </c>
       <c r="M233" t="n">
         <v>0</v>
@@ -23245,31 +23245,31 @@
         <v>0</v>
       </c>
       <c r="P233" t="n">
-        <v>-0.0738227920009401</v>
+        <v>-0.0791929877231321</v>
       </c>
       <c r="Q233" t="n">
-        <v>-0.0534816177231594</v>
+        <v>-0.0615128469594488</v>
       </c>
       <c r="R233" t="n">
-        <v>0.000203443356532583</v>
+        <v>0.000203037980052656</v>
       </c>
       <c r="S233" t="n">
-        <v>-0.00101889098104918</v>
+        <v>-0.00101686078217227</v>
       </c>
       <c r="T233" t="n">
-        <v>-0.000246709475946344</v>
+        <v>-0.000246217890141103</v>
       </c>
       <c r="U233" t="n">
-        <v>-0.00174188623205948</v>
+        <v>0.0225149866301508</v>
       </c>
       <c r="V233" t="n">
-        <v>-0.000243588812998019</v>
+        <v>-0.000245537329284517</v>
       </c>
       <c r="W233" t="n">
-        <v>-5.90629203205199</v>
+        <v>-5.99744240546112</v>
       </c>
       <c r="X233" t="n">
-        <v>-0.947120950463217</v>
+        <v>-0.958214967844601</v>
       </c>
       <c r="Y233" t="e">
         <v>#NUM!</v>
@@ -23278,19 +23278,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA233" t="n">
-        <v>5.9713656487234</v>
+        <v>11.6727840385583</v>
       </c>
       <c r="AB233" t="n">
-        <v>-15.2566839896174</v>
+        <v>-15.8716065544526</v>
       </c>
       <c r="AC233" t="n">
-        <v>-8.32844959134408</v>
+        <v>-2.2221443763655</v>
       </c>
       <c r="AD233" t="n">
         <v>0</v>
       </c>
       <c r="AE233" t="n">
-        <v>-5.56342539428815</v>
+        <v>-5.68257939950309</v>
       </c>
     </row>
     <row r="234">
@@ -23298,7 +23298,7 @@
         <v>265</v>
       </c>
       <c r="B234" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C234" t="n">
         <v>0</v>
@@ -23310,25 +23310,25 @@
         <v>#NUM!</v>
       </c>
       <c r="F234" t="n">
-        <v>3.6190399799111</v>
+        <v>3.8354944411779</v>
       </c>
       <c r="G234" t="n">
-        <v>2.04452940303916</v>
+        <v>2.07069044065283</v>
       </c>
       <c r="H234" t="n">
-        <v>0.228250090588388</v>
+        <v>0.227723792160673</v>
       </c>
       <c r="I234" t="n">
         <v>0</v>
       </c>
       <c r="J234" t="n">
-        <v>0.0785155806756128</v>
+        <v>0.0783576813629675</v>
       </c>
       <c r="K234" t="n">
-        <v>-6.88148463390872</v>
+        <v>-7.36430820297969</v>
       </c>
       <c r="L234" t="n">
-        <v>-0.722042677932606</v>
+        <v>-0.728095181603661</v>
       </c>
       <c r="M234" t="n">
         <v>0</v>
@@ -23340,31 +23340,31 @@
         <v>0</v>
       </c>
       <c r="P234" t="n">
-        <v>-0.0686750682417609</v>
+        <v>-0.0739572559884908</v>
       </c>
       <c r="Q234" t="n">
-        <v>-0.0516248439236888</v>
+        <v>-0.0589488506608058</v>
       </c>
       <c r="R234" t="n">
-        <v>0.000199746733948407</v>
+        <v>0.000199348723298747</v>
       </c>
       <c r="S234" t="n">
-        <v>-0.00102368783622513</v>
+        <v>-0.00102164807941644</v>
       </c>
       <c r="T234" t="n">
         <v>0</v>
       </c>
       <c r="U234" t="n">
-        <v>-0.00170995496904564</v>
+        <v>0.0207477666811622</v>
       </c>
       <c r="V234" t="n">
-        <v>-0.000239129527510748</v>
+        <v>-0.000241053557252871</v>
       </c>
       <c r="W234" t="n">
-        <v>-5.8832342610377</v>
+        <v>-5.97322864400373</v>
       </c>
       <c r="X234" t="n">
-        <v>-0.943430367024577</v>
+        <v>-0.95453096941944</v>
       </c>
       <c r="Y234" t="e">
         <v>#NUM!</v>
@@ -23373,19 +23373,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA234" t="n">
-        <v>5.87220670973692</v>
+        <v>6.1069989763434</v>
       </c>
       <c r="AB234" t="n">
-        <v>-15.2299649666933</v>
+        <v>-15.8617508994999</v>
       </c>
       <c r="AC234" t="n">
-        <v>-8.41934981094317</v>
+        <v>-8.73387771295107</v>
       </c>
       <c r="AD234" t="n">
         <v>0</v>
       </c>
       <c r="AE234" t="n">
-        <v>-5.43277097523112</v>
+        <v>-5.49302496854176</v>
       </c>
     </row>
     <row r="235">
@@ -23393,7 +23393,7 @@
         <v>266</v>
       </c>
       <c r="B235" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C235" t="n">
         <v>0</v>
@@ -23405,25 +23405,25 @@
         <v>#NUM!</v>
       </c>
       <c r="F235" t="n">
-        <v>3.57214368642037</v>
+        <v>3.79055198273087</v>
       </c>
       <c r="G235" t="n">
-        <v>2.02312068909619</v>
+        <v>2.04898897475753</v>
       </c>
       <c r="H235" t="n">
-        <v>0.230756391199535</v>
+        <v>0.01200446971962</v>
       </c>
       <c r="I235" t="n">
         <v>0</v>
       </c>
       <c r="J235" t="n">
-        <v>0.0760153144447605</v>
+        <v>0.00577502922181358</v>
       </c>
       <c r="K235" t="n">
-        <v>0</v>
+        <v>-7.26415941384648</v>
       </c>
       <c r="L235" t="n">
-        <v>0</v>
+        <v>-0.723925351762704</v>
       </c>
       <c r="M235" t="n">
         <v>0</v>
@@ -23435,31 +23435,31 @@
         <v>0</v>
       </c>
       <c r="P235" t="n">
-        <v>-0.0408478576513773</v>
+        <v>-0.069109569306645</v>
       </c>
       <c r="Q235" t="n">
-        <v>-0.0433266971651069</v>
+        <v>-0.0569848727572219</v>
       </c>
       <c r="R235" t="n">
-        <v>0.000195826610541586</v>
+        <v>0.000195436411083312</v>
       </c>
       <c r="S235" t="n">
-        <v>-0.000603910393540015</v>
+        <v>-0.000602707063401036</v>
       </c>
       <c r="T235" t="n">
         <v>0</v>
       </c>
       <c r="U235" t="n">
-        <v>-0.00134346462800481</v>
+        <v>0.0193266366341969</v>
       </c>
       <c r="V235" t="n">
-        <v>-0.0000802391209995042</v>
+        <v>-0.000236284647387811</v>
       </c>
       <c r="W235" t="n">
-        <v>0</v>
+        <v>-5.94178815237639</v>
       </c>
       <c r="X235" t="n">
-        <v>0</v>
+        <v>-0.948345967006404</v>
       </c>
       <c r="Y235" t="e">
         <v>#NUM!</v>
@@ -23468,19 +23468,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA235" t="n">
-        <v>5.80589854628874</v>
+        <v>5.77220772832667</v>
       </c>
       <c r="AB235" t="n">
-        <v>-0.0860268363079363</v>
+        <v>-15.7010578275158</v>
       </c>
       <c r="AC235" t="n">
-        <v>5.72524699647437</v>
+        <v>-8.97318656589395</v>
       </c>
       <c r="AD235" t="n">
         <v>0</v>
       </c>
       <c r="AE235" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>-5.33326240807133</v>
       </c>
     </row>
     <row r="236">
@@ -23488,7 +23488,7 @@
         <v>267</v>
       </c>
       <c r="B236" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C236" t="n">
         <v>0</v>
@@ -23500,19 +23500,19 @@
         <v>#NUM!</v>
       </c>
       <c r="F236" t="n">
-        <v>3.53302887178381</v>
+        <v>3.75364946940031</v>
       </c>
       <c r="G236" t="n">
-        <v>2.00423722863772</v>
+        <v>2.02982193615988</v>
       </c>
       <c r="H236" t="n">
-        <v>0.0722448881001593</v>
+        <v>0.068441052443647</v>
       </c>
       <c r="I236" t="n">
         <v>0</v>
       </c>
       <c r="J236" t="n">
-        <v>0.0747419081652842</v>
+        <v>0.0753030343302221</v>
       </c>
       <c r="K236" t="n">
         <v>0</v>
@@ -23530,25 +23530,25 @@
         <v>0</v>
       </c>
       <c r="P236" t="n">
-        <v>-0.0222951725289816</v>
+        <v>-0.0409446021188461</v>
       </c>
       <c r="Q236" t="n">
-        <v>-0.0423924734740165</v>
+        <v>-0.0494861451310024</v>
       </c>
       <c r="R236" t="n">
-        <v>0.000192353129506779</v>
+        <v>0.000191969851177877</v>
       </c>
       <c r="S236" t="n">
-        <v>-0.000602405522784614</v>
+        <v>-0.000601205191249771</v>
       </c>
       <c r="T236" t="n">
         <v>0</v>
       </c>
       <c r="U236" t="n">
-        <v>0</v>
+        <v>0.0123050377594143</v>
       </c>
       <c r="V236" t="n">
-        <v>-0.0000788141545999593</v>
+        <v>-0.0000794381856996428</v>
       </c>
       <c r="W236" t="n">
         <v>0</v>
@@ -23563,19 +23563,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA236" t="n">
-        <v>5.59952103983218</v>
+        <v>5.83603232485594</v>
       </c>
       <c r="AB236" t="n">
-        <v>-0.0651868979666943</v>
+        <v>-0.0786245472818299</v>
       </c>
       <c r="AC236" t="n">
-        <v>5.53825530337416</v>
+        <v>5.76236368088285</v>
       </c>
       <c r="AD236" t="n">
         <v>0</v>
       </c>
       <c r="AE236" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
@@ -23583,7 +23583,7 @@
         <v>268</v>
       </c>
       <c r="B237" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C237" t="n">
         <v>0</v>
@@ -23595,19 +23595,19 @@
         <v>#NUM!</v>
       </c>
       <c r="F237" t="n">
-        <v>3.49062824628225</v>
+        <v>3.71308723677001</v>
       </c>
       <c r="G237" t="n">
-        <v>1.98462400626479</v>
+        <v>2.00987654386104</v>
       </c>
       <c r="H237" t="n">
-        <v>0.0705331289343471</v>
+        <v>0.168761337795088</v>
       </c>
       <c r="I237" t="n">
         <v>0</v>
       </c>
       <c r="J237" t="n">
-        <v>0.0733085225613066</v>
+        <v>0.0738623383780963</v>
       </c>
       <c r="K237" t="n">
         <v>0</v>
@@ -23625,25 +23625,25 @@
         <v>0</v>
       </c>
       <c r="P237" t="n">
-        <v>-0.0219939670595133</v>
+        <v>-0.0221805559616482</v>
       </c>
       <c r="Q237" t="n">
-        <v>-0.0426909772840707</v>
+        <v>-0.0496523719061936</v>
       </c>
       <c r="R237" t="n">
-        <v>0.000444130220152017</v>
+        <v>0.00044324525510416</v>
       </c>
       <c r="S237" t="n">
-        <v>-0.00060261353165759</v>
+        <v>-0.000601412785644412</v>
       </c>
       <c r="T237" t="n">
         <v>0</v>
       </c>
       <c r="U237" t="n">
-        <v>0</v>
+        <v>0.0067906511762143</v>
       </c>
       <c r="V237" t="n">
-        <v>-0.0000773248506388465</v>
+        <v>-0.0000779406515372065</v>
       </c>
       <c r="W237" t="n">
         <v>0</v>
@@ -23658,19 +23658,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA237" t="n">
-        <v>5.53633467011732</v>
+        <v>5.87013291190953</v>
       </c>
       <c r="AB237" t="n">
-        <v>-0.0649308917620592</v>
+        <v>-0.0652850983851142</v>
       </c>
       <c r="AC237" t="n">
-        <v>5.47526336804371</v>
+        <v>5.80898554444588</v>
       </c>
       <c r="AD237" t="n">
         <v>0</v>
       </c>
       <c r="AE237" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238">
@@ -23678,7 +23678,7 @@
         <v>269</v>
       </c>
       <c r="B238" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C238" t="n">
         <v>0</v>
@@ -23690,19 +23690,19 @@
         <v>#NUM!</v>
       </c>
       <c r="F238" t="n">
-        <v>3.51824978588587</v>
+        <v>3.74715450723628</v>
       </c>
       <c r="G238" t="n">
-        <v>1.96748284330751</v>
+        <v>1.992435833953</v>
       </c>
       <c r="H238" t="n">
-        <v>0.171482084754022</v>
+        <v>0.164755970851461</v>
       </c>
       <c r="I238" t="n">
         <v>0</v>
       </c>
       <c r="J238" t="n">
-        <v>0.0720669216007551</v>
+        <v>0.0726139863270012</v>
       </c>
       <c r="K238" t="n">
         <v>0</v>
@@ -23720,25 +23720,25 @@
         <v>0</v>
       </c>
       <c r="P238" t="n">
-        <v>-0.0176903958017606</v>
+        <v>-0.0223716348361572</v>
       </c>
       <c r="Q238" t="n">
-        <v>-0.0425964117977141</v>
+        <v>-0.0494335661497027</v>
       </c>
       <c r="R238" t="n">
         <v>0</v>
       </c>
       <c r="S238" t="n">
-        <v>-0.0005034373075644</v>
+        <v>-0.000502434175721073</v>
       </c>
       <c r="T238" t="n">
         <v>0</v>
       </c>
       <c r="U238" t="n">
-        <v>0</v>
+        <v>0.00666686795572179</v>
       </c>
       <c r="V238" t="n">
-        <v>-0.0000759121767036513</v>
+        <v>-0.0000765206319916611</v>
       </c>
       <c r="W238" t="n">
         <v>0</v>
@@ -23753,19 +23753,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA238" t="n">
-        <v>5.64081814717383</v>
+        <v>5.88188411620007</v>
       </c>
       <c r="AB238" t="n">
-        <v>-0.0608745265794686</v>
+        <v>-0.0657243795167567</v>
       </c>
       <c r="AC238" t="n">
-        <v>5.58362599945893</v>
+        <v>5.82032792449831</v>
       </c>
       <c r="AD238" t="n">
         <v>0</v>
       </c>
       <c r="AE238" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
@@ -23773,7 +23773,7 @@
         <v>270</v>
       </c>
       <c r="B239" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C239" t="n">
         <v>0</v>
@@ -23785,19 +23785,19 @@
         <v>#NUM!</v>
       </c>
       <c r="F239" t="n">
-        <v>0</v>
+        <v>3.70000008665802</v>
       </c>
       <c r="G239" t="n">
-        <v>0</v>
+        <v>1.97243691333279</v>
       </c>
       <c r="H239" t="n">
-        <v>0.167276436644511</v>
+        <v>0.160731989143741</v>
       </c>
       <c r="I239" t="n">
         <v>0</v>
       </c>
       <c r="J239" t="n">
-        <v>0.0708528173192307</v>
+        <v>0.0713928120938873</v>
       </c>
       <c r="K239" t="n">
         <v>0</v>
@@ -23815,25 +23815,25 @@
         <v>0</v>
       </c>
       <c r="P239" t="n">
-        <v>0</v>
+        <v>-0.0179725615943227</v>
       </c>
       <c r="Q239" t="n">
-        <v>-0.0331251111958896</v>
+        <v>-0.0498288393681295</v>
       </c>
       <c r="R239" t="n">
         <v>0</v>
       </c>
       <c r="S239" t="n">
-        <v>-0.000397619271933572</v>
+        <v>-0.000396826988864878</v>
       </c>
       <c r="T239" t="n">
         <v>0</v>
       </c>
       <c r="U239" t="n">
-        <v>0</v>
+        <v>0.0052433347696283</v>
       </c>
       <c r="V239" t="n">
-        <v>0</v>
+        <v>-0.0000750771485229341</v>
       </c>
       <c r="W239" t="n">
         <v>0</v>
@@ -23848,19 +23848,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA239" t="n">
-        <v>0.238003495894634</v>
+        <v>5.81187607108815</v>
       </c>
       <c r="AB239" t="n">
-        <v>-0.0335228701561467</v>
+        <v>-0.0630360401465371</v>
       </c>
       <c r="AC239" t="n">
-        <v>0.204565278828774</v>
+        <v>5.7527862100638</v>
       </c>
       <c r="AD239" t="n">
         <v>0</v>
       </c>
       <c r="AE239" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
@@ -23868,7 +23868,7 @@
         <v>271</v>
       </c>
       <c r="B240" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C240" t="n">
         <v>0</v>
@@ -23886,13 +23886,13 @@
         <v>0</v>
       </c>
       <c r="H240" t="n">
-        <v>0.162979900079402</v>
+        <v>0.156616650878038</v>
       </c>
       <c r="I240" t="n">
         <v>0</v>
       </c>
       <c r="J240" t="n">
-        <v>0.0693811447220098</v>
+        <v>0.0699124281168817</v>
       </c>
       <c r="K240" t="n">
         <v>0</v>
@@ -23913,13 +23913,13 @@
         <v>0</v>
       </c>
       <c r="Q240" t="n">
-        <v>-0.032469415967349</v>
+        <v>-0.039504361764444</v>
       </c>
       <c r="R240" t="n">
         <v>0</v>
       </c>
       <c r="S240" t="n">
-        <v>-0.0002943395433199</v>
+        <v>-0.000293753051528703</v>
       </c>
       <c r="T240" t="n">
         <v>0</v>
@@ -23943,19 +23943,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA240" t="n">
-        <v>0.232241012889103</v>
+        <v>0.226412277898501</v>
       </c>
       <c r="AB240" t="n">
-        <v>-0.0327638569113506</v>
+        <v>-0.0397982385464291</v>
       </c>
       <c r="AC240" t="n">
-        <v>0.199557922250519</v>
+        <v>0.186710153598348</v>
       </c>
       <c r="AD240" t="n">
         <v>0</v>
       </c>
       <c r="AE240" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241">
@@ -23963,7 +23963,7 @@
         <v>272</v>
       </c>
       <c r="B241" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C241" t="n">
         <v>0</v>
@@ -23981,13 +23981,13 @@
         <v>0</v>
       </c>
       <c r="H241" t="n">
-        <v>0.158914143637246</v>
+        <v>0.152724102426152</v>
       </c>
       <c r="I241" t="n">
         <v>0</v>
       </c>
       <c r="J241" t="n">
-        <v>0.0681421391648267</v>
+        <v>0.0686656419318574</v>
       </c>
       <c r="K241" t="n">
         <v>0</v>
@@ -24008,13 +24008,13 @@
         <v>0</v>
       </c>
       <c r="Q241" t="n">
-        <v>-0.0323060619489991</v>
+        <v>-0.0392079562284777</v>
       </c>
       <c r="R241" t="n">
         <v>0</v>
       </c>
       <c r="S241" t="n">
-        <v>-0.000194233892271098</v>
+        <v>-0.000193846867566195</v>
       </c>
       <c r="T241" t="n">
         <v>0</v>
@@ -24038,19 +24038,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA241" t="n">
-        <v>0.22694137755605</v>
+        <v>0.221277918535408</v>
       </c>
       <c r="AB241" t="n">
-        <v>-0.0325003623948072</v>
+        <v>-0.0394018841038229</v>
       </c>
       <c r="AC241" t="n">
-        <v>0.19451927492442</v>
+        <v>0.181968999492182</v>
       </c>
       <c r="AD241" t="n">
         <v>0</v>
       </c>
       <c r="AE241" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
@@ -24058,7 +24058,7 @@
         <v>273</v>
       </c>
       <c r="B242" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C242" t="n">
         <v>0</v>
@@ -24076,13 +24076,13 @@
         <v>0</v>
       </c>
       <c r="H242" t="n">
-        <v>0.15953336701643</v>
+        <v>0.152850030377927</v>
       </c>
       <c r="I242" t="n">
         <v>0</v>
       </c>
       <c r="J242" t="n">
-        <v>0.066770105896176</v>
+        <v>0.0672866753263317</v>
       </c>
       <c r="K242" t="n">
         <v>0</v>
@@ -24103,13 +24103,13 @@
         <v>0</v>
       </c>
       <c r="Q242" t="n">
-        <v>-0.0314942307186923</v>
+        <v>-0.0382719464676964</v>
       </c>
       <c r="R242" t="n">
         <v>0</v>
       </c>
       <c r="S242" t="n">
-        <v>-0.0000969924932569386</v>
+        <v>-0.0000967992287459444</v>
       </c>
       <c r="T242" t="n">
         <v>0</v>
@@ -24133,19 +24133,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA242" t="n">
-        <v>0.22619059559475</v>
+        <v>0.220027183848495</v>
       </c>
       <c r="AB242" t="n">
-        <v>-0.0315912555671793</v>
+        <v>-0.0383687851293907</v>
       </c>
       <c r="AC242" t="n">
-        <v>0.194675056494781</v>
+        <v>0.181748292795029</v>
       </c>
       <c r="AD242" t="n">
         <v>0</v>
       </c>
       <c r="AE242" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
@@ -24153,7 +24153,7 @@
         <v>274</v>
       </c>
       <c r="B243" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C243" t="n">
         <v>0</v>
@@ -24171,13 +24171,13 @@
         <v>0</v>
       </c>
       <c r="H243" t="n">
-        <v>0</v>
+        <v>0.149226791444266</v>
       </c>
       <c r="I243" t="n">
         <v>0</v>
       </c>
       <c r="J243" t="n">
-        <v>0</v>
+        <v>0.0658542310726151</v>
       </c>
       <c r="K243" t="n">
         <v>0</v>
@@ -24198,7 +24198,7 @@
         <v>0</v>
       </c>
       <c r="Q243" t="n">
-        <v>-0.0105778525589836</v>
+        <v>-0.0375957467010318</v>
       </c>
       <c r="R243" t="n">
         <v>0</v>
@@ -24228,19 +24228,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA243" t="n">
-        <v>0</v>
+        <v>0.2149766183383</v>
       </c>
       <c r="AB243" t="n">
-        <v>-0.0105778525589836</v>
+        <v>-0.0375957467010318</v>
       </c>
       <c r="AC243" t="n">
-        <v>-0.0105778525589836</v>
+        <v>0.177466731163623</v>
       </c>
       <c r="AD243" t="n">
         <v>0</v>
       </c>
       <c r="AE243" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244">
@@ -24248,7 +24248,7 @@
         <v>275</v>
       </c>
       <c r="B244" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C244" t="n">
         <v>0</v>
@@ -24293,7 +24293,7 @@
         <v>0</v>
       </c>
       <c r="Q244" t="n">
-        <v>-0.0103698740124576</v>
+        <v>-0.0125990318901856</v>
       </c>
       <c r="R244" t="n">
         <v>0</v>
@@ -24326,16 +24326,16 @@
         <v>0</v>
       </c>
       <c r="AB244" t="n">
-        <v>-0.0103698740124576</v>
+        <v>-0.0125990318901856</v>
       </c>
       <c r="AC244" t="n">
-        <v>-0.0103698740124576</v>
+        <v>-0.0125990318901856</v>
       </c>
       <c r="AD244" t="n">
         <v>0</v>
       </c>
       <c r="AE244" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="245">
@@ -24343,7 +24343,7 @@
         <v>276</v>
       </c>
       <c r="B245" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C245" t="n">
         <v>0</v>
@@ -24388,7 +24388,7 @@
         <v>0</v>
       </c>
       <c r="Q245" t="n">
-        <v>-0.0101808000954974</v>
+        <v>-0.0123700239874886</v>
       </c>
       <c r="R245" t="n">
         <v>0</v>
@@ -24421,16 +24421,16 @@
         <v>0</v>
       </c>
       <c r="AB245" t="n">
-        <v>-0.0101808000954974</v>
+        <v>-0.0123700239874886</v>
       </c>
       <c r="AC245" t="n">
-        <v>-0.0101808000954974</v>
+        <v>-0.0123700239874886</v>
       </c>
       <c r="AD245" t="n">
         <v>0</v>
       </c>
       <c r="AE245" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
@@ -24438,7 +24438,7 @@
         <v>277</v>
       </c>
       <c r="B246" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C246" t="n">
         <v>0</v>
@@ -24483,7 +24483,7 @@
         <v>0</v>
       </c>
       <c r="Q246" t="n">
-        <v>-0.00998638791313794</v>
+        <v>-0.0121343766564271</v>
       </c>
       <c r="R246" t="n">
         <v>0</v>
@@ -24516,16 +24516,16 @@
         <v>0</v>
       </c>
       <c r="AB246" t="n">
-        <v>-0.00998638791313794</v>
+        <v>-0.0121343766564271</v>
       </c>
       <c r="AC246" t="n">
-        <v>-0.00998638791313794</v>
+        <v>-0.0121343766564271</v>
       </c>
       <c r="AD246" t="n">
         <v>0</v>
       </c>
       <c r="AE246" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
@@ -24533,7 +24533,7 @@
         <v>278</v>
       </c>
       <c r="B247" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C247" t="n">
         <v>0</v>
@@ -24578,7 +24578,7 @@
         <v>0</v>
       </c>
       <c r="Q247" t="n">
-        <v>0</v>
+        <v>-0.0119112091449515</v>
       </c>
       <c r="R247" t="n">
         <v>0</v>
@@ -24611,16 +24611,16 @@
         <v>0</v>
       </c>
       <c r="AB247" t="n">
-        <v>0</v>
+        <v>-0.0119112091449515</v>
       </c>
       <c r="AC247" t="n">
-        <v>0</v>
+        <v>-0.0119112091449515</v>
       </c>
       <c r="AD247" t="n">
         <v>0</v>
       </c>
       <c r="AE247" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
@@ -24628,7 +24628,7 @@
         <v>279</v>
       </c>
       <c r="B248" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C248" t="n">
         <v>0</v>
@@ -24715,7 +24715,7 @@
         <v>0</v>
       </c>
       <c r="AE248" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
@@ -24723,7 +24723,7 @@
         <v>280</v>
       </c>
       <c r="B249" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C249" t="n">
         <v>0</v>
@@ -24810,7 +24810,7 @@
         <v>0</v>
       </c>
       <c r="AE249" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
@@ -24818,7 +24818,7 @@
         <v>281</v>
       </c>
       <c r="B250" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C250" t="n">
         <v>0</v>
@@ -24905,7 +24905,7 @@
         <v>0</v>
       </c>
       <c r="AE250" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251">
@@ -24913,7 +24913,7 @@
         <v>282</v>
       </c>
       <c r="B251" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C251" t="n">
         <v>0</v>
@@ -25000,7 +25000,7 @@
         <v>0</v>
       </c>
       <c r="AE251" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252">
@@ -25008,7 +25008,7 @@
         <v>283</v>
       </c>
       <c r="B252" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C252" t="n">
         <v>0</v>
@@ -25095,7 +25095,7 @@
         <v>0</v>
       </c>
       <c r="AE252" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253">
@@ -25103,7 +25103,7 @@
         <v>284</v>
       </c>
       <c r="B253" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C253" t="n">
         <v>0</v>
@@ -25190,7 +25190,7 @@
         <v>0</v>
       </c>
       <c r="AE253" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254">
@@ -25198,7 +25198,7 @@
         <v>285</v>
       </c>
       <c r="B254" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C254" t="n">
         <v>0</v>
@@ -25285,7 +25285,7 @@
         <v>0</v>
       </c>
       <c r="AE254" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255">
@@ -25293,7 +25293,7 @@
         <v>286</v>
       </c>
       <c r="B255" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C255" t="n">
         <v>0</v>
@@ -25380,7 +25380,7 @@
         <v>0</v>
       </c>
       <c r="AE255" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256">
@@ -25388,7 +25388,7 @@
         <v>287</v>
       </c>
       <c r="B256" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C256" t="n">
         <v>0</v>
@@ -25475,7 +25475,7 @@
         <v>0</v>
       </c>
       <c r="AE256" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257">
@@ -25483,7 +25483,7 @@
         <v>288</v>
       </c>
       <c r="B257" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C257" t="n">
         <v>0</v>
@@ -25570,7 +25570,7 @@
         <v>0</v>
       </c>
       <c r="AE257" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258">
@@ -25578,7 +25578,7 @@
         <v>289</v>
       </c>
       <c r="B258" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C258" t="n">
         <v>0</v>
@@ -25665,7 +25665,7 @@
         <v>0</v>
       </c>
       <c r="AE258" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
@@ -25673,7 +25673,7 @@
         <v>290</v>
       </c>
       <c r="B259" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C259" t="n">
         <v>0</v>
@@ -25760,7 +25760,7 @@
         <v>0</v>
       </c>
       <c r="AE259" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260">
@@ -25768,7 +25768,7 @@
         <v>291</v>
       </c>
       <c r="B260" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C260" t="n">
         <v>0</v>
@@ -25855,7 +25855,7 @@
         <v>0</v>
       </c>
       <c r="AE260" t="n">
-        <v>0.000000000000000888178419700125</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
